--- a/data/censo_escolar_dataset/augmentation_method_results/censo_escolar_algorithm_with_paraphrasing_augmented_semantic_variation.xlsx
+++ b/data/censo_escolar_dataset/augmentation_method_results/censo_escolar_algorithm_with_paraphrasing_augmented_semantic_variation.xlsx
@@ -770,10 +770,10 @@
         <v>107</v>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0.2124567371627936</v>
+        <v>0.1653689888425294</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.2149952191818221</v>
+        <v>0.155309271617819</v>
       </c>
       <c r="D6" t="n">
         <v>5</v>
@@ -853,31 +853,31 @@
         <v>107</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.00545572229427993</v>
+        <v>0.001542117467544957</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.3910181333423479</v>
+        <v>0.1681621173616764</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.1216666821408425</v>
+        <v>0.05676154760542439</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.114944035606814</v>
+        <v>0.04953219146263699</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.08099872493263098</v>
+        <v>0.0379730298310586</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.04994725950868883</v>
+        <v>0.02499778583109086</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.1720245990225907</v>
+        <v>0.07577386651158918</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.2349982112860841</v>
+        <v>0.1117246175248639</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.2626877258795383</v>
+        <v>0.1313218377106815</v>
       </c>
     </row>
     <row r="12">
@@ -893,28 +893,28 @@
         <v>0</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.5596412961064696</v>
+        <v>0.5683522486864312</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.3032467921847448</v>
+        <v>0.2739764300796345</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.3046894104416529</v>
+        <v>0.2650686028320681</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.1349502210894539</v>
+        <v>0.1309836522017391</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.2021935953899522</v>
+        <v>0.1885399424284335</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.4033628058249402</v>
+        <v>0.3705992115621604</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.4831300028994988</v>
+        <v>0.4458035293735266</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.5132965434706683</v>
+        <v>0.4906233452849681</v>
       </c>
     </row>
     <row r="13">
@@ -927,31 +927,31 @@
         <v>107</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.002727861147139965</v>
+        <v>0.0007710587337724784</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.4322183745815764</v>
+        <v>0.3324900766620051</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.2124567371627936</v>
+        <v>0.1653689888425294</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.2149952191818221</v>
+        <v>0.155309271617819</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.101121118665643</v>
+        <v>0.07775610457322059</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.1342573640468928</v>
+        <v>0.114556406313505</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.2827736364405468</v>
+        <v>0.2275468161045712</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.3546502632140395</v>
+        <v>0.2693383861469911</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.3688220113123222</v>
+        <v>0.2892990197620025</v>
       </c>
     </row>
     <row r="15">
@@ -1003,16 +1003,16 @@
         <v>29</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.2101193270410776</v>
+        <v>0.1486689189845538</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.2155393529576363</v>
+        <v>0.1435399379835821</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.2956331561930912</v>
+        <v>0.2182015822387432</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.3238924334336508</v>
+        <v>0.2280417559683335</v>
       </c>
     </row>
     <row r="18">
@@ -1025,16 +1025,16 @@
         <v>46</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.2710215155069718</v>
+        <v>0.2148331282970106</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.2710046704098384</v>
+        <v>0.231249890018409</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.3673632118667438</v>
+        <v>0.2901995967753198</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.3752524128181346</v>
+        <v>0.3072210768957575</v>
       </c>
     </row>
     <row r="19">
@@ -1047,16 +1047,16 @@
         <v>8</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.1307895529777108</v>
+        <v>0.09149791272846297</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.1494496844102823</v>
+        <v>0.1273636087254706</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.2439298701511653</v>
+        <v>0.1579692252967436</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.3012351853935493</v>
+        <v>0.169139457716275</v>
       </c>
     </row>
     <row r="20">
@@ -1069,16 +1069,16 @@
         <v>24</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.1302543439618865</v>
+        <v>0.1153656646711831</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.121818516140826</v>
+        <v>0.113201877790298</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.2178819056422146</v>
+        <v>0.1743904935160301</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.2271341939346665</v>
+        <v>0.2030918547330574</v>
       </c>
     </row>
   </sheetData>
@@ -1211,31 +1211,31 @@
         <v>29</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.009177108301621995</v>
+        <v>0.01253394878377867</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.2642158389111164</v>
+        <v>0.1248171943003568</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.1189020031802196</v>
+        <v>0.05015700435375209</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.114944035606814</v>
+        <v>0.04688924644925674</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.06628388975576097</v>
+        <v>0.02515863767434402</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.07145806413193934</v>
+        <v>0.0312170400677072</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.1691362221266799</v>
+        <v>0.06440936671588116</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.1897536838942858</v>
+        <v>0.08076765640538885</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.2469284205192234</v>
+        <v>0.08661910318264886</v>
       </c>
     </row>
     <row r="7">
@@ -1253,31 +1253,31 @@
         <v>29</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>1.031619234481695e-12</v>
+        <v>0</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.503565019104802</v>
+        <v>0.4024297796108337</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.3013366509019356</v>
+        <v>0.2471808336153556</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.3042429843710823</v>
+        <v>0.2434733552805335</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.1091310893952658</v>
+        <v>0.09214066590028644</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.2303883561875507</v>
+        <v>0.2097655320913097</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.3749343560816256</v>
+        <v>0.3216018263283609</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.4265151012020558</v>
+        <v>0.366980997395599</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.4408375416869565</v>
+        <v>0.3785357636383119</v>
       </c>
     </row>
     <row r="8">
@@ -1295,31 +1295,31 @@
         <v>29</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.004588554151326807</v>
+        <v>0.02838366138606202</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.3838904290079592</v>
+        <v>0.2636234869555952</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.2101193270410776</v>
+        <v>0.1486689189845538</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.2155393529576363</v>
+        <v>0.1435399379835821</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.08122256737732776</v>
+        <v>0.05219200940393788</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.1476832389400284</v>
+        <v>0.1246377874190838</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.2753607172842387</v>
+        <v>0.182751750074537</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.2956331561930912</v>
+        <v>0.2182015822387432</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.3238924334336508</v>
+        <v>0.2280417559683335</v>
       </c>
     </row>
     <row r="9">
@@ -1337,31 +1337,31 @@
         <v>46</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.00956551253727389</v>
+        <v>0.003713468660734187</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.3910181333423479</v>
+        <v>0.1681621173616764</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.165093403450305</v>
+        <v>0.07672174141225746</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.1571954426587437</v>
+        <v>0.07245169580569921</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.07659562110129675</v>
+        <v>0.04134397758660753</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.1130351858147287</v>
+        <v>0.04872734912556698</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.1995672649339582</v>
+        <v>0.1040670291302611</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.2727833122407413</v>
+        <v>0.1334520288603656</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.3002019339263975</v>
+        <v>0.1487858387469762</v>
       </c>
     </row>
     <row r="10">
@@ -1379,31 +1379,31 @@
         <v>46</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>1.52566848043989e-12</v>
+        <v>8.215650382226158e-14</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.5596412961064696</v>
+        <v>0.5683522486864312</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.3769496275636387</v>
+        <v>0.3529445151817637</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.394135289750339</v>
+        <v>0.3719950261063286</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.1196844468896979</v>
+        <v>0.1248819037560548</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.3137772611987205</v>
+        <v>0.2948836580363199</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.467449390653163</v>
+        <v>0.4452101676882915</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.5146841058296631</v>
+        <v>0.4972233915715751</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.5362197551333727</v>
+        <v>0.5144190538433724</v>
       </c>
     </row>
     <row r="11">
@@ -1421,31 +1421,31 @@
         <v>46</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.004782756269399779</v>
+        <v>0.001856734330408172</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.4322183745815764</v>
+        <v>0.3324900766620051</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.2710215155069718</v>
+        <v>0.2148331282970106</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.2710046704098384</v>
+        <v>0.231249890018409</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.08677608140868591</v>
+        <v>0.07275796079911537</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.2189312631765307</v>
+        <v>0.1787480311708379</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.3421562553240357</v>
+        <v>0.2658774714822248</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.3673632118667438</v>
+        <v>0.2901995967753198</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.3752524128181346</v>
+        <v>0.3072210768957575</v>
       </c>
     </row>
     <row r="12">
@@ -1463,31 +1463,31 @@
         <v>8</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.00545572229427993</v>
+        <v>0.001542117467544957</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.2445387410812987</v>
+        <v>0.08058978715490661</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.07875808897947968</v>
+        <v>0.02556606454599071</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.03610579806822961</v>
+        <v>0.01730333303552101</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.083266022638979</v>
+        <v>0.02456332671077964</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.01263228083169204</v>
+        <v>0.009800898899583549</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.1334448381816842</v>
+        <v>0.03190921717399375</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.1879754153284134</v>
+        <v>0.05579013293846507</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.216257078204856</v>
+        <v>0.06818996004668583</v>
       </c>
     </row>
     <row r="13">
@@ -1508,28 +1508,28 @@
         <v>0</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.4725422601905683</v>
+        <v>0.3331276606072371</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.1828210169759419</v>
+        <v>0.1574297609109352</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.2099777176861</v>
+        <v>0.2084155540507066</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.1610754877042366</v>
+        <v>0.1281064014620159</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>8.603673329332651e-13</v>
+        <v>0</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.2756544114555761</v>
+        <v>0.2434918928500536</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.354420464275164</v>
+        <v>0.2940029326998693</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.4134813622328661</v>
+        <v>0.3135652966535532</v>
       </c>
     </row>
     <row r="14">
@@ -1547,31 +1547,31 @@
         <v>8</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.002727861147139965</v>
+        <v>0.0007710587337724784</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.3585405006359335</v>
+        <v>0.1803096901358065</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.1307895529777108</v>
+        <v>0.09149791272846297</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.1494496844102823</v>
+        <v>0.1273636087254706</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.1165297102082588</v>
+        <v>0.07016172200513605</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.006316140416276206</v>
+        <v>0.006032513648111665</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.1844149276265422</v>
+        <v>0.1411258736340061</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.2439298701511653</v>
+        <v>0.1579692252967436</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.3012351853935493</v>
+        <v>0.169139457716275</v>
       </c>
     </row>
     <row r="15">
@@ -1589,31 +1589,31 @@
         <v>24</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.007040395161529212</v>
+        <v>0.007950494394785457</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.1455318293110077</v>
+        <v>0.1067418824426338</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.05607565109557943</v>
+        <v>0.0368834935912429</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.04630830073064968</v>
+        <v>0.02508387110392146</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.04296091231740028</v>
+        <v>0.02550886799493819</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.01606581350649464</v>
+        <v>0.0200607302756729</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.08505957163469891</v>
+        <v>0.05889731492159009</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.1199854766854809</v>
+        <v>0.06620308774960021</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.1301937718496674</v>
+        <v>0.07858178021013436</v>
       </c>
     </row>
     <row r="16">
@@ -1631,31 +1631,31 @@
         <v>24</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.08703157686457874</v>
+        <v>0.05688012725004576</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.3628062257520536</v>
+        <v>0.4022340328314918</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.2044330368281937</v>
+        <v>0.1938478357511234</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.2006400795343415</v>
+        <v>0.188467049667605</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.07539728620061202</v>
+        <v>0.08427228165116918</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.1464723678093335</v>
+        <v>0.1483385272826203</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.2601682923320687</v>
+        <v>0.2454620240422427</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.3112041371419157</v>
+        <v>0.2968154894796385</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.3228298500571042</v>
+        <v>0.3128907252362373</v>
       </c>
     </row>
     <row r="17">
@@ -1673,31 +1673,31 @@
         <v>24</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.04924321965046258</v>
+        <v>0.03289598944293015</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.2297639960908038</v>
+        <v>0.2414558747877325</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.1302543439618865</v>
+        <v>0.1153656646711831</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.121818516140826</v>
+        <v>0.113201877790298</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.0556523119478078</v>
+        <v>0.05030531873086111</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.08341335923285548</v>
+        <v>0.09004255313281048</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.1662905613962053</v>
+        <v>0.1388777954847822</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.2178819056422146</v>
+        <v>0.1743904935160301</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.2271341939346665</v>
+        <v>0.2030918547330574</v>
       </c>
     </row>
   </sheetData>
@@ -1770,13 +1770,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>45</v>
+        <v>92</v>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D6" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>15</v>
+      </c>
+      <c r="C7" t="n">
+        <v>21</v>
+      </c>
+      <c r="D7" t="n">
         <v>46</v>
-      </c>
-      <c r="C7" t="n">
-        <v>19</v>
-      </c>
-      <c r="D7" t="n">
-        <v>32</v>
       </c>
     </row>
     <row r="8">
@@ -1802,13 +1802,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D8" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9">
@@ -1818,13 +1818,13 @@
         </is>
       </c>
       <c r="B9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" t="n">
+        <v>24</v>
+      </c>
+      <c r="D9" t="n">
         <v>4</v>
-      </c>
-      <c r="C9" t="n">
-        <v>28</v>
-      </c>
-      <c r="D9" t="n">
-        <v>22</v>
       </c>
     </row>
     <row r="10">
@@ -1837,10 +1837,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1853,7 +1853,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -2015,7 +2015,7 @@
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2023,13 +2023,13 @@
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.00545572229427993</v>
+        <v>0.001542117467544957</v>
       </c>
       <c r="F6" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.002727861147139965</v>
+        <v>0.0007710587337724784</v>
       </c>
     </row>
     <row r="7">
@@ -2042,7 +2042,7 @@
         <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2050,13 +2050,13 @@
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.005899750453198682</v>
+        <v>0.003102976661646273</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.002949875226599452</v>
+        <v>0.001551488330823136</v>
       </c>
     </row>
     <row r="8">
@@ -2069,21 +2069,21 @@
         <v>3</v>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Fácil</t>
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.009177108301621995</v>
+        <v>0.003713468660734187</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>1.031619234481695e-12</v>
+        <v>8.215650382226158e-14</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.004588554151326807</v>
+        <v>0.001856734330408172</v>
       </c>
     </row>
     <row r="9">
@@ -2096,21 +2096,21 @@
         <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Fácil</t>
+          <t>Difícil</t>
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.00956551253727389</v>
+        <v>0.01505237750774902</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>1.52566848043989e-12</v>
+        <v>0</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.004782756269399779</v>
+        <v>0.007526188753874508</v>
       </c>
     </row>
     <row r="10">
@@ -2123,21 +2123,21 @@
         <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Difícil</t>
+          <t>Média</t>
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.01487645762452317</v>
+        <v>0.05676732277212404</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>1.147082429042712e-12</v>
+        <v>0</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.007438228812835124</v>
+        <v>0.02838366138606202</v>
       </c>
     </row>
     <row r="11">
@@ -2150,7 +2150,7 @@
         <v>6</v>
       </c>
       <c r="C11" t="n">
-        <v>106</v>
+        <v>16</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2158,13 +2158,13 @@
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.01145486243634641</v>
+        <v>0.008911851635814538</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.08703157686457874</v>
+        <v>0.05688012725004576</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.04924321965046258</v>
+        <v>0.03289598944293015</v>
       </c>
     </row>
     <row r="12">
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.007817775614430089</v>
+        <v>0.01955819095508748</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.1094636815249135</v>
+        <v>0.05716118142296212</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.05864072856967179</v>
+        <v>0.0383596861890248</v>
       </c>
     </row>
     <row r="13">
@@ -2204,7 +2204,7 @@
         <v>8</v>
       </c>
       <c r="C13" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2212,13 +2212,13 @@
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.007040395161529212</v>
+        <v>0.0209719266014341</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.1244943878303318</v>
+        <v>0.06891771905604804</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.06576739149593053</v>
+        <v>0.04494482282874107</v>
       </c>
     </row>
     <row r="14">
@@ -2231,7 +2231,7 @@
         <v>9</v>
       </c>
       <c r="C14" t="n">
-        <v>15</v>
+        <v>106</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2239,13 +2239,13 @@
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.008221605795053932</v>
+        <v>0.02435717118061964</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.1293437653948696</v>
+        <v>0.07821603186249781</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.06878268559496176</v>
+        <v>0.05128660152155873</v>
       </c>
     </row>
     <row r="15">
@@ -2258,21 +2258,21 @@
         <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>97</v>
+        <v>25</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Muito Difícil</t>
+          <t>Média</t>
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.0124573657200947</v>
+        <v>0.01254466489204975</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.1413827489732095</v>
+        <v>0.1113385482187692</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.07692005734665208</v>
+        <v>0.06194160655540948</v>
       </c>
     </row>
     <row r="16">
@@ -2293,13 +2293,13 @@
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.3910181333423479</v>
+        <v>0.09662790463757898</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.4734186158208048</v>
+        <v>0.5683522486864312</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.4322183745815764</v>
+        <v>0.3324900766620051</v>
       </c>
     </row>
     <row r="17">
@@ -2312,21 +2312,21 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>20</v>
+        <v>83</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Fácil</t>
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.2642158389111164</v>
+        <v>0.1619195158229001</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.503565019104802</v>
+        <v>0.4750415320521104</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.3838904290079592</v>
+        <v>0.3184805239375053</v>
       </c>
     </row>
     <row r="18">
@@ -2339,7 +2339,7 @@
         <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2347,13 +2347,13 @@
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.3047119486854925</v>
+        <v>0.131151066136469</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.4495417151502377</v>
+        <v>0.4868278325874162</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.3771268319178651</v>
+        <v>0.3089894493619426</v>
       </c>
     </row>
     <row r="19">
@@ -2366,7 +2366,7 @@
         <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>40</v>
+        <v>73</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2374,13 +2374,13 @@
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.2466722832810408</v>
+        <v>0.07335830321890957</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.5057408368815099</v>
+        <v>0.5304736157754943</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.3762065600812754</v>
+        <v>0.301915959497202</v>
       </c>
     </row>
     <row r="20">
@@ -2393,7 +2393,7 @@
         <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>23</v>
+        <v>70</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2401,13 +2401,13 @@
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.3002500050701402</v>
+        <v>0.07055928788889421</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.4445299369872839</v>
+        <v>0.5099089895865478</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.3723899710287121</v>
+        <v>0.290234138737721</v>
       </c>
     </row>
     <row r="21">
@@ -2420,7 +2420,7 @@
         <v>6</v>
       </c>
       <c r="C21" t="n">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.2025541521736167</v>
+        <v>0.1491222528487269</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.5394662687877634</v>
+        <v>0.4312078567771102</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.3710102104806901</v>
+        <v>0.2901650548129185</v>
       </c>
     </row>
     <row r="22">
@@ -2447,7 +2447,7 @@
         <v>7</v>
       </c>
       <c r="C22" t="n">
-        <v>74</v>
+        <v>3</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2455,13 +2455,13 @@
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.2500596253277578</v>
+        <v>0.07235975306049902</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.4773728011778372</v>
+        <v>0.5021967895592312</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.3637162132527975</v>
+        <v>0.2872782713098651</v>
       </c>
     </row>
     <row r="23">
@@ -2474,7 +2474,7 @@
         <v>8</v>
       </c>
       <c r="C23" t="n">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2482,13 +2482,13 @@
         </is>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.1591442711755684</v>
+        <v>0.07858775943019125</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.5596412961064696</v>
+        <v>0.4922499935839191</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.359392783641019</v>
+        <v>0.2854188765070552</v>
       </c>
     </row>
     <row r="24">
@@ -2501,21 +2501,21 @@
         <v>9</v>
       </c>
       <c r="C24" t="n">
-        <v>9</v>
+        <v>71</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Difícil</t>
+          <t>Fácil</t>
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.2445387410812987</v>
+        <v>0.0540940923579265</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.4725422601905683</v>
+        <v>0.5159224085956473</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.3585405006359335</v>
+        <v>0.2850082504767869</v>
       </c>
     </row>
     <row r="25">
@@ -2528,7 +2528,7 @@
         <v>10</v>
       </c>
       <c r="C25" t="n">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2536,13 +2536,13 @@
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.200888203520164</v>
+        <v>0.1681621173616764</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.5140726106159141</v>
+        <v>0.3753532127939545</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.3574804070680391</v>
+        <v>0.2717576650778155</v>
       </c>
     </row>
   </sheetData>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>46256.9807175926</v>
+        <v>46237.90638888889</v>
       </c>
     </row>
     <row r="7">
@@ -2614,7 +2614,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>/home/isaquenascimento/ast-driven-data-augmentation-algorithm/data/censo_escolar_dataset/augmentation_method_results/censo_escolar_algorithm_with_paraphrasing_augmented.json</t>
+          <t>/home/ioolliver/Workspace/ast-driven-data-augmentation-algorithm/data/censo_escolar_dataset/augmentation_method_results/censo_escolar_algorithm_with_paraphrasing_augmented.json</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Qwen/Qwen3-Embedding-4B</t>
+          <t>jinaai/jina-embeddings-v3</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>symmetric text similarity</t>
+          <t>text-matching</t>
         </is>
       </c>
     </row>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>CC BY-NC 4.0</t>
         </is>
       </c>
     </row>
